--- a/ig/main/ValueSet-jdv-j402-type-droit-prestation-ms.xlsx
+++ b/ig/main/ValueSet-jdv-j402-type-droit-prestation-ms.xlsx
@@ -7,13 +7,14 @@
   </bookViews>
   <sheets>
     <sheet name="Metadata" r:id="rId3" sheetId="1"/>
-    <sheet name="Include #0" r:id="rId4" sheetId="2"/>
+    <sheet name="Expansion Parameters" r:id="rId4" sheetId="2"/>
+    <sheet name="Expansion" r:id="rId5" sheetId="3"/>
   </sheets>
 </workbook>
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="38" uniqueCount="35">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="415" uniqueCount="164">
   <si>
     <t>Property</t>
   </si>
@@ -66,15 +67,12 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-05-05T12:00:00.000+00:00</t>
+    <t>2026-05-29T09:12:29+00:00</t>
   </si>
   <si>
     <t>Publisher</t>
   </si>
   <si>
-    <t>Agence du Numérique en Santé (ANS) - 2-10 Rue d'Oradour-sur-Glane, 75015 Paris</t>
-  </si>
-  <si>
     <t>Jurisdiction</t>
   </si>
   <si>
@@ -84,9 +82,6 @@
     <t>Description</t>
   </si>
   <si>
-    <t>Type de droit et prestation caractérisant la décision d'orientation.</t>
-  </si>
-  <si>
     <t>Purpose</t>
   </si>
   <si>
@@ -99,25 +94,418 @@
     <t>BooleanType[null]</t>
   </si>
   <si>
-    <t>Operation</t>
-  </si>
-  <si>
-    <t>niveau</t>
-  </si>
-  <si>
-    <t>=</t>
-  </si>
-  <si>
-    <t>2</t>
-  </si>
-  <si>
-    <t/>
-  </si>
-  <si>
-    <t>System URI</t>
+    <t>Parameter</t>
+  </si>
+  <si>
+    <t>used-codesystem</t>
+  </si>
+  <si>
+    <t>https://smt.esante.gouv.fr/fhir/CodeSystem/tre-r420-droit-prestation|20260505120000</t>
+  </si>
+  <si>
+    <t>version</t>
+  </si>
+  <si>
+    <t>warning-draft</t>
+  </si>
+  <si>
+    <t>https://smt.esante.gouv.fr/fhir/ValueSet/jdv-j402-type-droit-prestation-ms|20260505120000</t>
+  </si>
+  <si>
+    <t>Level</t>
+  </si>
+  <si>
+    <t>System</t>
+  </si>
+  <si>
+    <t>Code</t>
+  </si>
+  <si>
+    <t>Display</t>
+  </si>
+  <si>
+    <t>Abstract</t>
+  </si>
+  <si>
+    <t>Inactive</t>
+  </si>
+  <si>
+    <t>1</t>
   </si>
   <si>
     <t>https://smt.esante.gouv.fr/fhir/CodeSystem/tre-r420-droit-prestation</t>
+  </si>
+  <si>
+    <t>1.1</t>
+  </si>
+  <si>
+    <t>AAH L.821-1</t>
+  </si>
+  <si>
+    <t>1.2</t>
+  </si>
+  <si>
+    <t>AAH L.821-2</t>
+  </si>
+  <si>
+    <t>10.1</t>
+  </si>
+  <si>
+    <t>Accompagnant des élèves en situation de handicap (AESH) - aide individuelle</t>
+  </si>
+  <si>
+    <t>10.2</t>
+  </si>
+  <si>
+    <t>Accompagnant des élèves en situation de handicap (AESH) - aide mutualisée</t>
+  </si>
+  <si>
+    <t>2.1</t>
+  </si>
+  <si>
+    <t>ACFP (Allocation compensatrice pour frais professionnels)</t>
+  </si>
+  <si>
+    <t>2.2</t>
+  </si>
+  <si>
+    <t>ACTP (Allocation compensatrice pour tierce personne)</t>
+  </si>
+  <si>
+    <t>6.1</t>
+  </si>
+  <si>
+    <t>AEEH de base</t>
+  </si>
+  <si>
+    <t>11.7</t>
+  </si>
+  <si>
+    <t>Aide à l'insertion professionnelle - Subvention d'installation</t>
+  </si>
+  <si>
+    <t>4.2</t>
+  </si>
+  <si>
+    <t>Carte mobilité inclusion, Mention invalidité</t>
+  </si>
+  <si>
+    <t>4.3</t>
+  </si>
+  <si>
+    <t>Carte mobilité inclusion, Mention priorité</t>
+  </si>
+  <si>
+    <t>4.1</t>
+  </si>
+  <si>
+    <t>Carte mobilité inclusion, Mention stationnement</t>
+  </si>
+  <si>
+    <t>6.2</t>
+  </si>
+  <si>
+    <t>Complément 1 de l'AEEH</t>
+  </si>
+  <si>
+    <t>6.3</t>
+  </si>
+  <si>
+    <t>Complément 2 de l'AEEH</t>
+  </si>
+  <si>
+    <t>6.4</t>
+  </si>
+  <si>
+    <t>Complément 3 de l'AEEH</t>
+  </si>
+  <si>
+    <t>6.5</t>
+  </si>
+  <si>
+    <t>Complément 4 de l'AEEH</t>
+  </si>
+  <si>
+    <t>6.6</t>
+  </si>
+  <si>
+    <t>Complément 5 de l'AEEH</t>
+  </si>
+  <si>
+    <t>6.7</t>
+  </si>
+  <si>
+    <t>Complément 6 de l'AEEH</t>
+  </si>
+  <si>
+    <t>8.3</t>
+  </si>
+  <si>
+    <t>Orientation en Enseignement adapté (SEGPA/EREA)</t>
+  </si>
+  <si>
+    <t>8.1</t>
+  </si>
+  <si>
+    <t>Orientation en enseignement ordinaire</t>
+  </si>
+  <si>
+    <t>11.5</t>
+  </si>
+  <si>
+    <t>Orientation en Etablissement et service d'accompagnement par le travail (ESAT)</t>
+  </si>
+  <si>
+    <t>11.2</t>
+  </si>
+  <si>
+    <t>Orientation en Etablissement ou service de préorientation (ESPO)</t>
+  </si>
+  <si>
+    <t>11.1</t>
+  </si>
+  <si>
+    <t>Orientation en Etablissement ou service de réadaptation professionnelle (ESRP)</t>
+  </si>
+  <si>
+    <t>8.6</t>
+  </si>
+  <si>
+    <t>Orientation en Unité d'enseignement</t>
+  </si>
+  <si>
+    <t>8.4</t>
+  </si>
+  <si>
+    <t>Orientation en Unité localisée pour l'inclusion scolaire (ULIS)</t>
+  </si>
+  <si>
+    <t>11.3</t>
+  </si>
+  <si>
+    <t>Orientation vers l'unité d'évaluation, de réentrainement et d'orientation sociale et socioprofessionnelle pour personnes cérébro-lésées (UEROS)</t>
+  </si>
+  <si>
+    <t>7.7</t>
+  </si>
+  <si>
+    <t>Orientation vers le dispositif ITEP</t>
+  </si>
+  <si>
+    <t>7.12</t>
+  </si>
+  <si>
+    <t>Orientation vers Service de soins et d'aide à domicile (SSAD)</t>
+  </si>
+  <si>
+    <t>13.99</t>
+  </si>
+  <si>
+    <t>Orientation vers un autre établissement ou service médico-social Adultes</t>
+  </si>
+  <si>
+    <t>7.99</t>
+  </si>
+  <si>
+    <t>Orientation vers un autre établissement ou service médico-social Enfants</t>
+  </si>
+  <si>
+    <t>13.2</t>
+  </si>
+  <si>
+    <t>Orientation vers un Etablissement d'accueil médicalisé en tout ou partie</t>
+  </si>
+  <si>
+    <t>13.1</t>
+  </si>
+  <si>
+    <t>Orientation vers un Etablissement d'accueil non médicalisé</t>
+  </si>
+  <si>
+    <t>7.2</t>
+  </si>
+  <si>
+    <t>Orientation vers un Institut d'éducation motrice (IEM)</t>
+  </si>
+  <si>
+    <t>7.13</t>
+  </si>
+  <si>
+    <t>Orientation vers un Institut d'éducation sensorielle (IES)</t>
+  </si>
+  <si>
+    <t>7.1</t>
+  </si>
+  <si>
+    <t>Orientation vers un Institut médico-éducatif (IME)</t>
+  </si>
+  <si>
+    <t>7.3</t>
+  </si>
+  <si>
+    <t>Orientation vers un institut pour personnes avec une déficience auditive</t>
+  </si>
+  <si>
+    <t>7.4</t>
+  </si>
+  <si>
+    <t>Orientation vers un institut pour personnes avec une déficience visuelle</t>
+  </si>
+  <si>
+    <t>7.6</t>
+  </si>
+  <si>
+    <t>Orientation vers un Institut thérapeutique, éducatif et pédagogique (ITEP)</t>
+  </si>
+  <si>
+    <t>8.9</t>
+  </si>
+  <si>
+    <t>Orientation vers un Pôle d'enseignement jeune sourd (PEJS)</t>
+  </si>
+  <si>
+    <t>7.9</t>
+  </si>
+  <si>
+    <t>Orientation vers un Service d'accompagnement familial et d'éducation précoce (SAFEP)</t>
+  </si>
+  <si>
+    <t>13.5</t>
+  </si>
+  <si>
+    <t>Orientation vers un Service d'accompagnement médico-social pour adultes handicapés (SAMSAH)</t>
+  </si>
+  <si>
+    <t>13.4</t>
+  </si>
+  <si>
+    <t>Orientation vers un Service d'accompagnement à la vie sociale (SAVS)</t>
+  </si>
+  <si>
+    <t>7.11</t>
+  </si>
+  <si>
+    <t>Orientation vers un Service d'aide à l'acquisition de l'autonomie et à la scolarisation (SAAAS)</t>
+  </si>
+  <si>
+    <t>7.8</t>
+  </si>
+  <si>
+    <t>Orientation vers un Service d'éducation spéciale et de soins à domicile (SESSAD)</t>
+  </si>
+  <si>
+    <t>7.10</t>
+  </si>
+  <si>
+    <t>Orientation vers un Service de soutien à l'éducation familiale et à la scolarisation (SSEFS)</t>
+  </si>
+  <si>
+    <t>8.11</t>
+  </si>
+  <si>
+    <t>Orientation vers un établissement d'autorégulation</t>
+  </si>
+  <si>
+    <t>7.5</t>
+  </si>
+  <si>
+    <t>Orientation vers un établissement pour enfants ou adolescents polyhandicapés</t>
+  </si>
+  <si>
+    <t>13.3</t>
+  </si>
+  <si>
+    <t>Orientation vers une Maison d'accueil spécialisée (MAS)</t>
+  </si>
+  <si>
+    <t>11.6</t>
+  </si>
+  <si>
+    <t>Orientation vers une plateforme d'emploi accompagné</t>
+  </si>
+  <si>
+    <t>8.7</t>
+  </si>
+  <si>
+    <t>Orientation vers une Scolarisation en milieu ordinaire à temps partagé (UE et établissement scolaire)</t>
+  </si>
+  <si>
+    <t>8.10</t>
+  </si>
+  <si>
+    <t>Orientation vers une unité d'enseignement et une scolarisation en enseignement adapté à temps partagé</t>
+  </si>
+  <si>
+    <t>8.8</t>
+  </si>
+  <si>
+    <t>Orientation vers une Unité d'enseignement et une scolarisation en ULIS à temps partagé</t>
+  </si>
+  <si>
+    <t>5.1</t>
+  </si>
+  <si>
+    <t>PCH - élément 1 - Aide humaine</t>
+  </si>
+  <si>
+    <t>5.2</t>
+  </si>
+  <si>
+    <t>PCH - élément 2 - Aides techniques</t>
+  </si>
+  <si>
+    <t>5.3</t>
+  </si>
+  <si>
+    <t>PCH - élément 3 - Aménagement du logement</t>
+  </si>
+  <si>
+    <t>5.4</t>
+  </si>
+  <si>
+    <t>PCH - élément 3 - Aménagement du véhicule</t>
+  </si>
+  <si>
+    <t>5.5</t>
+  </si>
+  <si>
+    <t>PCH - élément 3 - Surcoûts liés au transport</t>
+  </si>
+  <si>
+    <t>5.7</t>
+  </si>
+  <si>
+    <t>PCH - élément 4 - Charges exceptionnelles</t>
+  </si>
+  <si>
+    <t>5.6</t>
+  </si>
+  <si>
+    <t>PCH - élément 4 - Charges spécifiques</t>
+  </si>
+  <si>
+    <t>5.8</t>
+  </si>
+  <si>
+    <t>PCH - élément 5 - Aide animalière</t>
+  </si>
+  <si>
+    <t>5.9</t>
+  </si>
+  <si>
+    <t>PCH 1 - Aide humaine à la parentalité</t>
+  </si>
+  <si>
+    <t>5.10</t>
+  </si>
+  <si>
+    <t>PCH 2 - Aides techniques à la parentalité</t>
+  </si>
+  <si>
+    <t>8.2</t>
+  </si>
+  <si>
+    <t>Redoublement en maternelle</t>
   </si>
 </sst>
 </file>
@@ -334,44 +722,40 @@
       <c r="A10" t="s" s="2">
         <v>18</v>
       </c>
-      <c r="B10" t="s" s="2">
-        <v>19</v>
-      </c>
+      <c r="B10" s="2"/>
     </row>
     <row r="11">
       <c r="A11" t="s" s="2">
+        <v>19</v>
+      </c>
+      <c r="B11" t="s" s="2">
         <v>20</v>
-      </c>
-      <c r="B11" t="s" s="2">
-        <v>21</v>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="s" s="2">
-        <v>22</v>
-      </c>
-      <c r="B12" t="s" s="2">
-        <v>23</v>
-      </c>
+        <v>21</v>
+      </c>
+      <c r="B12" s="2"/>
     </row>
     <row r="13">
       <c r="A13" t="s" s="2">
-        <v>24</v>
+        <v>22</v>
       </c>
       <c r="B13" s="2"/>
     </row>
     <row r="14">
       <c r="A14" t="s" s="2">
-        <v>25</v>
+        <v>23</v>
       </c>
       <c r="B14" s="2"/>
     </row>
     <row r="15">
       <c r="A15" t="s" s="2">
-        <v>26</v>
+        <v>24</v>
       </c>
       <c r="B15" t="s" s="2">
-        <v>27</v>
+        <v>25</v>
       </c>
     </row>
   </sheetData>
@@ -381,49 +765,1382 @@
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <dimension ref="A1:C4"/>
+  <dimension ref="A1:B5"/>
   <sheetFormatPr defaultRowHeight="15.0"/>
-  <cols>
-    <col min="1" max="1" width="30.703125" customWidth="true"/>
-    <col min="2" max="2" width="50.703125" customWidth="true"/>
-  </cols>
   <sheetData>
     <row r="1">
       <c r="A1" t="s" s="1">
-        <v>0</v>
+        <v>26</v>
       </c>
       <c r="B1" t="s" s="1">
-        <v>28</v>
-      </c>
-      <c r="C1" t="s" s="1">
         <v>1</v>
       </c>
     </row>
     <row r="2">
       <c r="A2" t="s" s="2">
-        <v>29</v>
+        <v>27</v>
       </c>
       <c r="B2" t="s" s="2">
-        <v>30</v>
-      </c>
-      <c r="C2" t="s" s="2">
-        <v>31</v>
+        <v>28</v>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="s" s="2">
-        <v>32</v>
+        <v>29</v>
       </c>
       <c r="B3" t="s" s="2">
-        <v>32</v>
+        <v>28</v>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="s" s="2">
+        <v>30</v>
+      </c>
+      <c r="B4" t="s" s="2">
+        <v>28</v>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" t="s" s="2">
+        <v>30</v>
+      </c>
+      <c r="B5" t="s" s="2">
+        <v>31</v>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins bottom="0.75" footer="0.3" header="0.3" left="0.7" right="0.7" top="0.75"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <dimension ref="A1:G63"/>
+  <sheetFormatPr defaultRowHeight="15.0"/>
+  <sheetData>
+    <row r="1">
+      <c r="A1" t="s" s="1">
+        <v>32</v>
+      </c>
+      <c r="B1" t="s" s="1">
         <v>33</v>
       </c>
+      <c r="C1" t="s" s="1">
+        <v>29</v>
+      </c>
+      <c r="D1" t="s" s="1">
+        <v>34</v>
+      </c>
+      <c r="E1" t="s" s="1">
+        <v>35</v>
+      </c>
+      <c r="F1" t="s" s="1">
+        <v>36</v>
+      </c>
+      <c r="G1" t="s" s="1">
+        <v>37</v>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" t="s" s="2">
+        <v>38</v>
+      </c>
+      <c r="B2" t="s" s="2">
+        <v>39</v>
+      </c>
+      <c r="C2" s="2"/>
+      <c r="D2" t="s" s="2">
+        <v>40</v>
+      </c>
+      <c r="E2" t="s" s="2">
+        <v>41</v>
+      </c>
+      <c r="F2" t="s" s="2">
+        <v>15</v>
+      </c>
+      <c r="G2" t="s" s="2">
+        <v>15</v>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" t="s" s="2">
+        <v>38</v>
+      </c>
+      <c r="B3" t="s" s="2">
+        <v>39</v>
+      </c>
+      <c r="C3" s="2"/>
+      <c r="D3" t="s" s="2">
+        <v>42</v>
+      </c>
+      <c r="E3" t="s" s="2">
+        <v>43</v>
+      </c>
+      <c r="F3" t="s" s="2">
+        <v>15</v>
+      </c>
+      <c r="G3" t="s" s="2">
+        <v>15</v>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" t="s" s="2">
+        <v>38</v>
+      </c>
       <c r="B4" t="s" s="2">
-        <v>34</v>
+        <v>39</v>
+      </c>
+      <c r="C4" s="2"/>
+      <c r="D4" t="s" s="2">
+        <v>44</v>
+      </c>
+      <c r="E4" t="s" s="2">
+        <v>45</v>
+      </c>
+      <c r="F4" t="s" s="2">
+        <v>15</v>
+      </c>
+      <c r="G4" t="s" s="2">
+        <v>15</v>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" t="s" s="2">
+        <v>38</v>
+      </c>
+      <c r="B5" t="s" s="2">
+        <v>39</v>
+      </c>
+      <c r="C5" s="2"/>
+      <c r="D5" t="s" s="2">
+        <v>46</v>
+      </c>
+      <c r="E5" t="s" s="2">
+        <v>47</v>
+      </c>
+      <c r="F5" t="s" s="2">
+        <v>15</v>
+      </c>
+      <c r="G5" t="s" s="2">
+        <v>15</v>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" t="s" s="2">
+        <v>38</v>
+      </c>
+      <c r="B6" t="s" s="2">
+        <v>39</v>
+      </c>
+      <c r="C6" s="2"/>
+      <c r="D6" t="s" s="2">
+        <v>48</v>
+      </c>
+      <c r="E6" t="s" s="2">
+        <v>49</v>
+      </c>
+      <c r="F6" t="s" s="2">
+        <v>15</v>
+      </c>
+      <c r="G6" t="s" s="2">
+        <v>15</v>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" t="s" s="2">
+        <v>38</v>
+      </c>
+      <c r="B7" t="s" s="2">
+        <v>39</v>
+      </c>
+      <c r="C7" s="2"/>
+      <c r="D7" t="s" s="2">
+        <v>50</v>
+      </c>
+      <c r="E7" t="s" s="2">
+        <v>51</v>
+      </c>
+      <c r="F7" t="s" s="2">
+        <v>15</v>
+      </c>
+      <c r="G7" t="s" s="2">
+        <v>15</v>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" t="s" s="2">
+        <v>38</v>
+      </c>
+      <c r="B8" t="s" s="2">
+        <v>39</v>
+      </c>
+      <c r="C8" s="2"/>
+      <c r="D8" t="s" s="2">
+        <v>52</v>
+      </c>
+      <c r="E8" t="s" s="2">
+        <v>53</v>
+      </c>
+      <c r="F8" t="s" s="2">
+        <v>15</v>
+      </c>
+      <c r="G8" t="s" s="2">
+        <v>15</v>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" t="s" s="2">
+        <v>38</v>
+      </c>
+      <c r="B9" t="s" s="2">
+        <v>39</v>
+      </c>
+      <c r="C9" s="2"/>
+      <c r="D9" t="s" s="2">
+        <v>54</v>
+      </c>
+      <c r="E9" t="s" s="2">
+        <v>55</v>
+      </c>
+      <c r="F9" t="s" s="2">
+        <v>15</v>
+      </c>
+      <c r="G9" t="s" s="2">
+        <v>15</v>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" t="s" s="2">
+        <v>38</v>
+      </c>
+      <c r="B10" t="s" s="2">
+        <v>39</v>
+      </c>
+      <c r="C10" s="2"/>
+      <c r="D10" t="s" s="2">
+        <v>56</v>
+      </c>
+      <c r="E10" t="s" s="2">
+        <v>57</v>
+      </c>
+      <c r="F10" t="s" s="2">
+        <v>15</v>
+      </c>
+      <c r="G10" t="s" s="2">
+        <v>15</v>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" t="s" s="2">
+        <v>38</v>
+      </c>
+      <c r="B11" t="s" s="2">
+        <v>39</v>
+      </c>
+      <c r="C11" s="2"/>
+      <c r="D11" t="s" s="2">
+        <v>58</v>
+      </c>
+      <c r="E11" t="s" s="2">
+        <v>59</v>
+      </c>
+      <c r="F11" t="s" s="2">
+        <v>15</v>
+      </c>
+      <c r="G11" t="s" s="2">
+        <v>15</v>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" t="s" s="2">
+        <v>38</v>
+      </c>
+      <c r="B12" t="s" s="2">
+        <v>39</v>
+      </c>
+      <c r="C12" s="2"/>
+      <c r="D12" t="s" s="2">
+        <v>60</v>
+      </c>
+      <c r="E12" t="s" s="2">
+        <v>61</v>
+      </c>
+      <c r="F12" t="s" s="2">
+        <v>15</v>
+      </c>
+      <c r="G12" t="s" s="2">
+        <v>15</v>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" t="s" s="2">
+        <v>38</v>
+      </c>
+      <c r="B13" t="s" s="2">
+        <v>39</v>
+      </c>
+      <c r="C13" s="2"/>
+      <c r="D13" t="s" s="2">
+        <v>62</v>
+      </c>
+      <c r="E13" t="s" s="2">
+        <v>63</v>
+      </c>
+      <c r="F13" t="s" s="2">
+        <v>15</v>
+      </c>
+      <c r="G13" t="s" s="2">
+        <v>15</v>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" t="s" s="2">
+        <v>38</v>
+      </c>
+      <c r="B14" t="s" s="2">
+        <v>39</v>
+      </c>
+      <c r="C14" s="2"/>
+      <c r="D14" t="s" s="2">
+        <v>64</v>
+      </c>
+      <c r="E14" t="s" s="2">
+        <v>65</v>
+      </c>
+      <c r="F14" t="s" s="2">
+        <v>15</v>
+      </c>
+      <c r="G14" t="s" s="2">
+        <v>15</v>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" t="s" s="2">
+        <v>38</v>
+      </c>
+      <c r="B15" t="s" s="2">
+        <v>39</v>
+      </c>
+      <c r="C15" s="2"/>
+      <c r="D15" t="s" s="2">
+        <v>66</v>
+      </c>
+      <c r="E15" t="s" s="2">
+        <v>67</v>
+      </c>
+      <c r="F15" t="s" s="2">
+        <v>15</v>
+      </c>
+      <c r="G15" t="s" s="2">
+        <v>15</v>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" t="s" s="2">
+        <v>38</v>
+      </c>
+      <c r="B16" t="s" s="2">
+        <v>39</v>
+      </c>
+      <c r="C16" s="2"/>
+      <c r="D16" t="s" s="2">
+        <v>68</v>
+      </c>
+      <c r="E16" t="s" s="2">
+        <v>69</v>
+      </c>
+      <c r="F16" t="s" s="2">
+        <v>15</v>
+      </c>
+      <c r="G16" t="s" s="2">
+        <v>15</v>
+      </c>
+    </row>
+    <row r="17">
+      <c r="A17" t="s" s="2">
+        <v>38</v>
+      </c>
+      <c r="B17" t="s" s="2">
+        <v>39</v>
+      </c>
+      <c r="C17" s="2"/>
+      <c r="D17" t="s" s="2">
+        <v>70</v>
+      </c>
+      <c r="E17" t="s" s="2">
+        <v>71</v>
+      </c>
+      <c r="F17" t="s" s="2">
+        <v>15</v>
+      </c>
+      <c r="G17" t="s" s="2">
+        <v>15</v>
+      </c>
+    </row>
+    <row r="18">
+      <c r="A18" t="s" s="2">
+        <v>38</v>
+      </c>
+      <c r="B18" t="s" s="2">
+        <v>39</v>
+      </c>
+      <c r="C18" s="2"/>
+      <c r="D18" t="s" s="2">
+        <v>72</v>
+      </c>
+      <c r="E18" t="s" s="2">
+        <v>73</v>
+      </c>
+      <c r="F18" t="s" s="2">
+        <v>15</v>
+      </c>
+      <c r="G18" t="s" s="2">
+        <v>15</v>
+      </c>
+    </row>
+    <row r="19">
+      <c r="A19" t="s" s="2">
+        <v>38</v>
+      </c>
+      <c r="B19" t="s" s="2">
+        <v>39</v>
+      </c>
+      <c r="C19" s="2"/>
+      <c r="D19" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="E19" t="s" s="2">
+        <v>75</v>
+      </c>
+      <c r="F19" t="s" s="2">
+        <v>15</v>
+      </c>
+      <c r="G19" t="s" s="2">
+        <v>15</v>
+      </c>
+    </row>
+    <row r="20">
+      <c r="A20" t="s" s="2">
+        <v>38</v>
+      </c>
+      <c r="B20" t="s" s="2">
+        <v>39</v>
+      </c>
+      <c r="C20" s="2"/>
+      <c r="D20" t="s" s="2">
+        <v>76</v>
+      </c>
+      <c r="E20" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="F20" t="s" s="2">
+        <v>15</v>
+      </c>
+      <c r="G20" t="s" s="2">
+        <v>15</v>
+      </c>
+    </row>
+    <row r="21">
+      <c r="A21" t="s" s="2">
+        <v>38</v>
+      </c>
+      <c r="B21" t="s" s="2">
+        <v>39</v>
+      </c>
+      <c r="C21" s="2"/>
+      <c r="D21" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="E21" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="F21" t="s" s="2">
+        <v>15</v>
+      </c>
+      <c r="G21" t="s" s="2">
+        <v>15</v>
+      </c>
+    </row>
+    <row r="22">
+      <c r="A22" t="s" s="2">
+        <v>38</v>
+      </c>
+      <c r="B22" t="s" s="2">
+        <v>39</v>
+      </c>
+      <c r="C22" s="2"/>
+      <c r="D22" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="E22" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="F22" t="s" s="2">
+        <v>15</v>
+      </c>
+      <c r="G22" t="s" s="2">
+        <v>15</v>
+      </c>
+    </row>
+    <row r="23">
+      <c r="A23" t="s" s="2">
+        <v>38</v>
+      </c>
+      <c r="B23" t="s" s="2">
+        <v>39</v>
+      </c>
+      <c r="C23" s="2"/>
+      <c r="D23" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="E23" t="s" s="2">
+        <v>83</v>
+      </c>
+      <c r="F23" t="s" s="2">
+        <v>15</v>
+      </c>
+      <c r="G23" t="s" s="2">
+        <v>15</v>
+      </c>
+    </row>
+    <row r="24">
+      <c r="A24" t="s" s="2">
+        <v>38</v>
+      </c>
+      <c r="B24" t="s" s="2">
+        <v>39</v>
+      </c>
+      <c r="C24" s="2"/>
+      <c r="D24" t="s" s="2">
+        <v>84</v>
+      </c>
+      <c r="E24" t="s" s="2">
+        <v>85</v>
+      </c>
+      <c r="F24" t="s" s="2">
+        <v>15</v>
+      </c>
+      <c r="G24" t="s" s="2">
+        <v>15</v>
+      </c>
+    </row>
+    <row r="25">
+      <c r="A25" t="s" s="2">
+        <v>38</v>
+      </c>
+      <c r="B25" t="s" s="2">
+        <v>39</v>
+      </c>
+      <c r="C25" s="2"/>
+      <c r="D25" t="s" s="2">
+        <v>86</v>
+      </c>
+      <c r="E25" t="s" s="2">
+        <v>87</v>
+      </c>
+      <c r="F25" t="s" s="2">
+        <v>15</v>
+      </c>
+      <c r="G25" t="s" s="2">
+        <v>15</v>
+      </c>
+    </row>
+    <row r="26">
+      <c r="A26" t="s" s="2">
+        <v>38</v>
+      </c>
+      <c r="B26" t="s" s="2">
+        <v>39</v>
+      </c>
+      <c r="C26" s="2"/>
+      <c r="D26" t="s" s="2">
+        <v>88</v>
+      </c>
+      <c r="E26" t="s" s="2">
+        <v>89</v>
+      </c>
+      <c r="F26" t="s" s="2">
+        <v>15</v>
+      </c>
+      <c r="G26" t="s" s="2">
+        <v>15</v>
+      </c>
+    </row>
+    <row r="27">
+      <c r="A27" t="s" s="2">
+        <v>38</v>
+      </c>
+      <c r="B27" t="s" s="2">
+        <v>39</v>
+      </c>
+      <c r="C27" s="2"/>
+      <c r="D27" t="s" s="2">
+        <v>90</v>
+      </c>
+      <c r="E27" t="s" s="2">
+        <v>91</v>
+      </c>
+      <c r="F27" t="s" s="2">
+        <v>15</v>
+      </c>
+      <c r="G27" t="s" s="2">
+        <v>15</v>
+      </c>
+    </row>
+    <row r="28">
+      <c r="A28" t="s" s="2">
+        <v>38</v>
+      </c>
+      <c r="B28" t="s" s="2">
+        <v>39</v>
+      </c>
+      <c r="C28" s="2"/>
+      <c r="D28" t="s" s="2">
+        <v>92</v>
+      </c>
+      <c r="E28" t="s" s="2">
+        <v>93</v>
+      </c>
+      <c r="F28" t="s" s="2">
+        <v>15</v>
+      </c>
+      <c r="G28" t="s" s="2">
+        <v>15</v>
+      </c>
+    </row>
+    <row r="29">
+      <c r="A29" t="s" s="2">
+        <v>38</v>
+      </c>
+      <c r="B29" t="s" s="2">
+        <v>39</v>
+      </c>
+      <c r="C29" s="2"/>
+      <c r="D29" t="s" s="2">
+        <v>94</v>
+      </c>
+      <c r="E29" t="s" s="2">
+        <v>95</v>
+      </c>
+      <c r="F29" t="s" s="2">
+        <v>15</v>
+      </c>
+      <c r="G29" t="s" s="2">
+        <v>15</v>
+      </c>
+    </row>
+    <row r="30">
+      <c r="A30" t="s" s="2">
+        <v>38</v>
+      </c>
+      <c r="B30" t="s" s="2">
+        <v>39</v>
+      </c>
+      <c r="C30" s="2"/>
+      <c r="D30" t="s" s="2">
+        <v>96</v>
+      </c>
+      <c r="E30" t="s" s="2">
+        <v>97</v>
+      </c>
+      <c r="F30" t="s" s="2">
+        <v>15</v>
+      </c>
+      <c r="G30" t="s" s="2">
+        <v>15</v>
+      </c>
+    </row>
+    <row r="31">
+      <c r="A31" t="s" s="2">
+        <v>38</v>
+      </c>
+      <c r="B31" t="s" s="2">
+        <v>39</v>
+      </c>
+      <c r="C31" s="2"/>
+      <c r="D31" t="s" s="2">
+        <v>98</v>
+      </c>
+      <c r="E31" t="s" s="2">
+        <v>99</v>
+      </c>
+      <c r="F31" t="s" s="2">
+        <v>15</v>
+      </c>
+      <c r="G31" t="s" s="2">
+        <v>15</v>
+      </c>
+    </row>
+    <row r="32">
+      <c r="A32" t="s" s="2">
+        <v>38</v>
+      </c>
+      <c r="B32" t="s" s="2">
+        <v>39</v>
+      </c>
+      <c r="C32" s="2"/>
+      <c r="D32" t="s" s="2">
+        <v>100</v>
+      </c>
+      <c r="E32" t="s" s="2">
+        <v>101</v>
+      </c>
+      <c r="F32" t="s" s="2">
+        <v>15</v>
+      </c>
+      <c r="G32" t="s" s="2">
+        <v>15</v>
+      </c>
+    </row>
+    <row r="33">
+      <c r="A33" t="s" s="2">
+        <v>38</v>
+      </c>
+      <c r="B33" t="s" s="2">
+        <v>39</v>
+      </c>
+      <c r="C33" s="2"/>
+      <c r="D33" t="s" s="2">
+        <v>102</v>
+      </c>
+      <c r="E33" t="s" s="2">
+        <v>103</v>
+      </c>
+      <c r="F33" t="s" s="2">
+        <v>15</v>
+      </c>
+      <c r="G33" t="s" s="2">
+        <v>15</v>
+      </c>
+    </row>
+    <row r="34">
+      <c r="A34" t="s" s="2">
+        <v>38</v>
+      </c>
+      <c r="B34" t="s" s="2">
+        <v>39</v>
+      </c>
+      <c r="C34" s="2"/>
+      <c r="D34" t="s" s="2">
+        <v>104</v>
+      </c>
+      <c r="E34" t="s" s="2">
+        <v>105</v>
+      </c>
+      <c r="F34" t="s" s="2">
+        <v>15</v>
+      </c>
+      <c r="G34" t="s" s="2">
+        <v>15</v>
+      </c>
+    </row>
+    <row r="35">
+      <c r="A35" t="s" s="2">
+        <v>38</v>
+      </c>
+      <c r="B35" t="s" s="2">
+        <v>39</v>
+      </c>
+      <c r="C35" s="2"/>
+      <c r="D35" t="s" s="2">
+        <v>106</v>
+      </c>
+      <c r="E35" t="s" s="2">
+        <v>107</v>
+      </c>
+      <c r="F35" t="s" s="2">
+        <v>15</v>
+      </c>
+      <c r="G35" t="s" s="2">
+        <v>15</v>
+      </c>
+    </row>
+    <row r="36">
+      <c r="A36" t="s" s="2">
+        <v>38</v>
+      </c>
+      <c r="B36" t="s" s="2">
+        <v>39</v>
+      </c>
+      <c r="C36" s="2"/>
+      <c r="D36" t="s" s="2">
+        <v>108</v>
+      </c>
+      <c r="E36" t="s" s="2">
+        <v>109</v>
+      </c>
+      <c r="F36" t="s" s="2">
+        <v>15</v>
+      </c>
+      <c r="G36" t="s" s="2">
+        <v>15</v>
+      </c>
+    </row>
+    <row r="37">
+      <c r="A37" t="s" s="2">
+        <v>38</v>
+      </c>
+      <c r="B37" t="s" s="2">
+        <v>39</v>
+      </c>
+      <c r="C37" s="2"/>
+      <c r="D37" t="s" s="2">
+        <v>110</v>
+      </c>
+      <c r="E37" t="s" s="2">
+        <v>111</v>
+      </c>
+      <c r="F37" t="s" s="2">
+        <v>15</v>
+      </c>
+      <c r="G37" t="s" s="2">
+        <v>15</v>
+      </c>
+    </row>
+    <row r="38">
+      <c r="A38" t="s" s="2">
+        <v>38</v>
+      </c>
+      <c r="B38" t="s" s="2">
+        <v>39</v>
+      </c>
+      <c r="C38" s="2"/>
+      <c r="D38" t="s" s="2">
+        <v>112</v>
+      </c>
+      <c r="E38" t="s" s="2">
+        <v>113</v>
+      </c>
+      <c r="F38" t="s" s="2">
+        <v>15</v>
+      </c>
+      <c r="G38" t="s" s="2">
+        <v>15</v>
+      </c>
+    </row>
+    <row r="39">
+      <c r="A39" t="s" s="2">
+        <v>38</v>
+      </c>
+      <c r="B39" t="s" s="2">
+        <v>39</v>
+      </c>
+      <c r="C39" s="2"/>
+      <c r="D39" t="s" s="2">
+        <v>114</v>
+      </c>
+      <c r="E39" t="s" s="2">
+        <v>115</v>
+      </c>
+      <c r="F39" t="s" s="2">
+        <v>15</v>
+      </c>
+      <c r="G39" t="s" s="2">
+        <v>15</v>
+      </c>
+    </row>
+    <row r="40">
+      <c r="A40" t="s" s="2">
+        <v>38</v>
+      </c>
+      <c r="B40" t="s" s="2">
+        <v>39</v>
+      </c>
+      <c r="C40" s="2"/>
+      <c r="D40" t="s" s="2">
+        <v>116</v>
+      </c>
+      <c r="E40" t="s" s="2">
+        <v>117</v>
+      </c>
+      <c r="F40" t="s" s="2">
+        <v>15</v>
+      </c>
+      <c r="G40" t="s" s="2">
+        <v>15</v>
+      </c>
+    </row>
+    <row r="41">
+      <c r="A41" t="s" s="2">
+        <v>38</v>
+      </c>
+      <c r="B41" t="s" s="2">
+        <v>39</v>
+      </c>
+      <c r="C41" s="2"/>
+      <c r="D41" t="s" s="2">
+        <v>118</v>
+      </c>
+      <c r="E41" t="s" s="2">
+        <v>119</v>
+      </c>
+      <c r="F41" t="s" s="2">
+        <v>15</v>
+      </c>
+      <c r="G41" t="s" s="2">
+        <v>15</v>
+      </c>
+    </row>
+    <row r="42">
+      <c r="A42" t="s" s="2">
+        <v>38</v>
+      </c>
+      <c r="B42" t="s" s="2">
+        <v>39</v>
+      </c>
+      <c r="C42" s="2"/>
+      <c r="D42" t="s" s="2">
+        <v>120</v>
+      </c>
+      <c r="E42" t="s" s="2">
+        <v>121</v>
+      </c>
+      <c r="F42" t="s" s="2">
+        <v>15</v>
+      </c>
+      <c r="G42" t="s" s="2">
+        <v>15</v>
+      </c>
+    </row>
+    <row r="43">
+      <c r="A43" t="s" s="2">
+        <v>38</v>
+      </c>
+      <c r="B43" t="s" s="2">
+        <v>39</v>
+      </c>
+      <c r="C43" s="2"/>
+      <c r="D43" t="s" s="2">
+        <v>122</v>
+      </c>
+      <c r="E43" t="s" s="2">
+        <v>123</v>
+      </c>
+      <c r="F43" t="s" s="2">
+        <v>15</v>
+      </c>
+      <c r="G43" t="s" s="2">
+        <v>15</v>
+      </c>
+    </row>
+    <row r="44">
+      <c r="A44" t="s" s="2">
+        <v>38</v>
+      </c>
+      <c r="B44" t="s" s="2">
+        <v>39</v>
+      </c>
+      <c r="C44" s="2"/>
+      <c r="D44" t="s" s="2">
+        <v>124</v>
+      </c>
+      <c r="E44" t="s" s="2">
+        <v>125</v>
+      </c>
+      <c r="F44" t="s" s="2">
+        <v>15</v>
+      </c>
+      <c r="G44" t="s" s="2">
+        <v>15</v>
+      </c>
+    </row>
+    <row r="45">
+      <c r="A45" t="s" s="2">
+        <v>38</v>
+      </c>
+      <c r="B45" t="s" s="2">
+        <v>39</v>
+      </c>
+      <c r="C45" s="2"/>
+      <c r="D45" t="s" s="2">
+        <v>126</v>
+      </c>
+      <c r="E45" t="s" s="2">
+        <v>127</v>
+      </c>
+      <c r="F45" t="s" s="2">
+        <v>15</v>
+      </c>
+      <c r="G45" t="s" s="2">
+        <v>15</v>
+      </c>
+    </row>
+    <row r="46">
+      <c r="A46" t="s" s="2">
+        <v>38</v>
+      </c>
+      <c r="B46" t="s" s="2">
+        <v>39</v>
+      </c>
+      <c r="C46" s="2"/>
+      <c r="D46" t="s" s="2">
+        <v>128</v>
+      </c>
+      <c r="E46" t="s" s="2">
+        <v>129</v>
+      </c>
+      <c r="F46" t="s" s="2">
+        <v>15</v>
+      </c>
+      <c r="G46" t="s" s="2">
+        <v>15</v>
+      </c>
+    </row>
+    <row r="47">
+      <c r="A47" t="s" s="2">
+        <v>38</v>
+      </c>
+      <c r="B47" t="s" s="2">
+        <v>39</v>
+      </c>
+      <c r="C47" s="2"/>
+      <c r="D47" t="s" s="2">
+        <v>130</v>
+      </c>
+      <c r="E47" t="s" s="2">
+        <v>131</v>
+      </c>
+      <c r="F47" t="s" s="2">
+        <v>15</v>
+      </c>
+      <c r="G47" t="s" s="2">
+        <v>15</v>
+      </c>
+    </row>
+    <row r="48">
+      <c r="A48" t="s" s="2">
+        <v>38</v>
+      </c>
+      <c r="B48" t="s" s="2">
+        <v>39</v>
+      </c>
+      <c r="C48" s="2"/>
+      <c r="D48" t="s" s="2">
+        <v>132</v>
+      </c>
+      <c r="E48" t="s" s="2">
+        <v>133</v>
+      </c>
+      <c r="F48" t="s" s="2">
+        <v>15</v>
+      </c>
+      <c r="G48" t="s" s="2">
+        <v>15</v>
+      </c>
+    </row>
+    <row r="49">
+      <c r="A49" t="s" s="2">
+        <v>38</v>
+      </c>
+      <c r="B49" t="s" s="2">
+        <v>39</v>
+      </c>
+      <c r="C49" s="2"/>
+      <c r="D49" t="s" s="2">
+        <v>134</v>
+      </c>
+      <c r="E49" t="s" s="2">
+        <v>135</v>
+      </c>
+      <c r="F49" t="s" s="2">
+        <v>15</v>
+      </c>
+      <c r="G49" t="s" s="2">
+        <v>15</v>
+      </c>
+    </row>
+    <row r="50">
+      <c r="A50" t="s" s="2">
+        <v>38</v>
+      </c>
+      <c r="B50" t="s" s="2">
+        <v>39</v>
+      </c>
+      <c r="C50" s="2"/>
+      <c r="D50" t="s" s="2">
+        <v>136</v>
+      </c>
+      <c r="E50" t="s" s="2">
+        <v>137</v>
+      </c>
+      <c r="F50" t="s" s="2">
+        <v>15</v>
+      </c>
+      <c r="G50" t="s" s="2">
+        <v>15</v>
+      </c>
+    </row>
+    <row r="51">
+      <c r="A51" t="s" s="2">
+        <v>38</v>
+      </c>
+      <c r="B51" t="s" s="2">
+        <v>39</v>
+      </c>
+      <c r="C51" s="2"/>
+      <c r="D51" t="s" s="2">
+        <v>138</v>
+      </c>
+      <c r="E51" t="s" s="2">
+        <v>139</v>
+      </c>
+      <c r="F51" t="s" s="2">
+        <v>15</v>
+      </c>
+      <c r="G51" t="s" s="2">
+        <v>15</v>
+      </c>
+    </row>
+    <row r="52">
+      <c r="A52" t="s" s="2">
+        <v>38</v>
+      </c>
+      <c r="B52" t="s" s="2">
+        <v>39</v>
+      </c>
+      <c r="C52" s="2"/>
+      <c r="D52" t="s" s="2">
+        <v>140</v>
+      </c>
+      <c r="E52" t="s" s="2">
+        <v>141</v>
+      </c>
+      <c r="F52" t="s" s="2">
+        <v>15</v>
+      </c>
+      <c r="G52" t="s" s="2">
+        <v>15</v>
+      </c>
+    </row>
+    <row r="53">
+      <c r="A53" t="s" s="2">
+        <v>38</v>
+      </c>
+      <c r="B53" t="s" s="2">
+        <v>39</v>
+      </c>
+      <c r="C53" s="2"/>
+      <c r="D53" t="s" s="2">
+        <v>142</v>
+      </c>
+      <c r="E53" t="s" s="2">
+        <v>143</v>
+      </c>
+      <c r="F53" t="s" s="2">
+        <v>15</v>
+      </c>
+      <c r="G53" t="s" s="2">
+        <v>15</v>
+      </c>
+    </row>
+    <row r="54">
+      <c r="A54" t="s" s="2">
+        <v>38</v>
+      </c>
+      <c r="B54" t="s" s="2">
+        <v>39</v>
+      </c>
+      <c r="C54" s="2"/>
+      <c r="D54" t="s" s="2">
+        <v>144</v>
+      </c>
+      <c r="E54" t="s" s="2">
+        <v>145</v>
+      </c>
+      <c r="F54" t="s" s="2">
+        <v>15</v>
+      </c>
+      <c r="G54" t="s" s="2">
+        <v>15</v>
+      </c>
+    </row>
+    <row r="55">
+      <c r="A55" t="s" s="2">
+        <v>38</v>
+      </c>
+      <c r="B55" t="s" s="2">
+        <v>39</v>
+      </c>
+      <c r="C55" s="2"/>
+      <c r="D55" t="s" s="2">
+        <v>146</v>
+      </c>
+      <c r="E55" t="s" s="2">
+        <v>147</v>
+      </c>
+      <c r="F55" t="s" s="2">
+        <v>15</v>
+      </c>
+      <c r="G55" t="s" s="2">
+        <v>15</v>
+      </c>
+    </row>
+    <row r="56">
+      <c r="A56" t="s" s="2">
+        <v>38</v>
+      </c>
+      <c r="B56" t="s" s="2">
+        <v>39</v>
+      </c>
+      <c r="C56" s="2"/>
+      <c r="D56" t="s" s="2">
+        <v>148</v>
+      </c>
+      <c r="E56" t="s" s="2">
+        <v>149</v>
+      </c>
+      <c r="F56" t="s" s="2">
+        <v>15</v>
+      </c>
+      <c r="G56" t="s" s="2">
+        <v>15</v>
+      </c>
+    </row>
+    <row r="57">
+      <c r="A57" t="s" s="2">
+        <v>38</v>
+      </c>
+      <c r="B57" t="s" s="2">
+        <v>39</v>
+      </c>
+      <c r="C57" s="2"/>
+      <c r="D57" t="s" s="2">
+        <v>150</v>
+      </c>
+      <c r="E57" t="s" s="2">
+        <v>151</v>
+      </c>
+      <c r="F57" t="s" s="2">
+        <v>15</v>
+      </c>
+      <c r="G57" t="s" s="2">
+        <v>15</v>
+      </c>
+    </row>
+    <row r="58">
+      <c r="A58" t="s" s="2">
+        <v>38</v>
+      </c>
+      <c r="B58" t="s" s="2">
+        <v>39</v>
+      </c>
+      <c r="C58" s="2"/>
+      <c r="D58" t="s" s="2">
+        <v>152</v>
+      </c>
+      <c r="E58" t="s" s="2">
+        <v>153</v>
+      </c>
+      <c r="F58" t="s" s="2">
+        <v>15</v>
+      </c>
+      <c r="G58" t="s" s="2">
+        <v>15</v>
+      </c>
+    </row>
+    <row r="59">
+      <c r="A59" t="s" s="2">
+        <v>38</v>
+      </c>
+      <c r="B59" t="s" s="2">
+        <v>39</v>
+      </c>
+      <c r="C59" s="2"/>
+      <c r="D59" t="s" s="2">
+        <v>154</v>
+      </c>
+      <c r="E59" t="s" s="2">
+        <v>155</v>
+      </c>
+      <c r="F59" t="s" s="2">
+        <v>15</v>
+      </c>
+      <c r="G59" t="s" s="2">
+        <v>15</v>
+      </c>
+    </row>
+    <row r="60">
+      <c r="A60" t="s" s="2">
+        <v>38</v>
+      </c>
+      <c r="B60" t="s" s="2">
+        <v>39</v>
+      </c>
+      <c r="C60" s="2"/>
+      <c r="D60" t="s" s="2">
+        <v>156</v>
+      </c>
+      <c r="E60" t="s" s="2">
+        <v>157</v>
+      </c>
+      <c r="F60" t="s" s="2">
+        <v>15</v>
+      </c>
+      <c r="G60" t="s" s="2">
+        <v>15</v>
+      </c>
+    </row>
+    <row r="61">
+      <c r="A61" t="s" s="2">
+        <v>38</v>
+      </c>
+      <c r="B61" t="s" s="2">
+        <v>39</v>
+      </c>
+      <c r="C61" s="2"/>
+      <c r="D61" t="s" s="2">
+        <v>158</v>
+      </c>
+      <c r="E61" t="s" s="2">
+        <v>159</v>
+      </c>
+      <c r="F61" t="s" s="2">
+        <v>15</v>
+      </c>
+      <c r="G61" t="s" s="2">
+        <v>15</v>
+      </c>
+    </row>
+    <row r="62">
+      <c r="A62" t="s" s="2">
+        <v>38</v>
+      </c>
+      <c r="B62" t="s" s="2">
+        <v>39</v>
+      </c>
+      <c r="C62" s="2"/>
+      <c r="D62" t="s" s="2">
+        <v>160</v>
+      </c>
+      <c r="E62" t="s" s="2">
+        <v>161</v>
+      </c>
+      <c r="F62" t="s" s="2">
+        <v>15</v>
+      </c>
+      <c r="G62" t="s" s="2">
+        <v>15</v>
+      </c>
+    </row>
+    <row r="63">
+      <c r="A63" t="s" s="2">
+        <v>38</v>
+      </c>
+      <c r="B63" t="s" s="2">
+        <v>39</v>
+      </c>
+      <c r="C63" s="2"/>
+      <c r="D63" t="s" s="2">
+        <v>162</v>
+      </c>
+      <c r="E63" t="s" s="2">
+        <v>163</v>
+      </c>
+      <c r="F63" t="s" s="2">
+        <v>15</v>
+      </c>
+      <c r="G63" t="s" s="2">
+        <v>15</v>
       </c>
     </row>
   </sheetData>

--- a/ig/main/ValueSet-jdv-j402-type-droit-prestation-ms.xlsx
+++ b/ig/main/ValueSet-jdv-j402-type-droit-prestation-ms.xlsx
@@ -8,12 +8,14 @@
   <sheets>
     <sheet name="Metadata" r:id="rId3" sheetId="1"/>
     <sheet name="Include #0" r:id="rId4" sheetId="2"/>
+    <sheet name="Expansion Parameters" r:id="rId5" sheetId="3"/>
+    <sheet name="Expansion" r:id="rId6" sheetId="4"/>
   </sheets>
 </workbook>
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="38" uniqueCount="35">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="425" uniqueCount="171">
   <si>
     <t>Property</t>
   </si>
@@ -118,6 +120,414 @@
   </si>
   <si>
     <t>https://smt.esante.gouv.fr/fhir/CodeSystem/tre-r420-droit-prestation</t>
+  </si>
+  <si>
+    <t>Parameter</t>
+  </si>
+  <si>
+    <t>used-codesystem</t>
+  </si>
+  <si>
+    <t>https://smt.esante.gouv.fr/fhir/CodeSystem/tre-r420-droit-prestation|20260505120000</t>
+  </si>
+  <si>
+    <t>version</t>
+  </si>
+  <si>
+    <t>warning-draft</t>
+  </si>
+  <si>
+    <t>Level</t>
+  </si>
+  <si>
+    <t>System</t>
+  </si>
+  <si>
+    <t>Code</t>
+  </si>
+  <si>
+    <t>Display</t>
+  </si>
+  <si>
+    <t>Abstract</t>
+  </si>
+  <si>
+    <t>Inactive</t>
+  </si>
+  <si>
+    <t>1</t>
+  </si>
+  <si>
+    <t>1.1</t>
+  </si>
+  <si>
+    <t>AAH L.821-1</t>
+  </si>
+  <si>
+    <t>1.2</t>
+  </si>
+  <si>
+    <t>AAH L.821-2</t>
+  </si>
+  <si>
+    <t>10.1</t>
+  </si>
+  <si>
+    <t>Accompagnant des élèves en situation de handicap (AESH) - aide individuelle</t>
+  </si>
+  <si>
+    <t>10.2</t>
+  </si>
+  <si>
+    <t>Accompagnant des élèves en situation de handicap (AESH) - aide mutualisée</t>
+  </si>
+  <si>
+    <t>2.1</t>
+  </si>
+  <si>
+    <t>ACFP (Allocation compensatrice pour frais professionnels)</t>
+  </si>
+  <si>
+    <t>2.2</t>
+  </si>
+  <si>
+    <t>ACTP (Allocation compensatrice pour tierce personne)</t>
+  </si>
+  <si>
+    <t>6.1</t>
+  </si>
+  <si>
+    <t>AEEH de base</t>
+  </si>
+  <si>
+    <t>11.7</t>
+  </si>
+  <si>
+    <t>Aide à l'insertion professionnelle - Subvention d'installation</t>
+  </si>
+  <si>
+    <t>4.2</t>
+  </si>
+  <si>
+    <t>Carte mobilité inclusion, Mention invalidité</t>
+  </si>
+  <si>
+    <t>4.3</t>
+  </si>
+  <si>
+    <t>Carte mobilité inclusion, Mention priorité</t>
+  </si>
+  <si>
+    <t>4.1</t>
+  </si>
+  <si>
+    <t>Carte mobilité inclusion, Mention stationnement</t>
+  </si>
+  <si>
+    <t>6.2</t>
+  </si>
+  <si>
+    <t>Complément 1 de l'AEEH</t>
+  </si>
+  <si>
+    <t>6.3</t>
+  </si>
+  <si>
+    <t>Complément 2 de l'AEEH</t>
+  </si>
+  <si>
+    <t>6.4</t>
+  </si>
+  <si>
+    <t>Complément 3 de l'AEEH</t>
+  </si>
+  <si>
+    <t>6.5</t>
+  </si>
+  <si>
+    <t>Complément 4 de l'AEEH</t>
+  </si>
+  <si>
+    <t>6.6</t>
+  </si>
+  <si>
+    <t>Complément 5 de l'AEEH</t>
+  </si>
+  <si>
+    <t>6.7</t>
+  </si>
+  <si>
+    <t>Complément 6 de l'AEEH</t>
+  </si>
+  <si>
+    <t>8.3</t>
+  </si>
+  <si>
+    <t>Orientation en Enseignement adapté (SEGPA/EREA)</t>
+  </si>
+  <si>
+    <t>8.1</t>
+  </si>
+  <si>
+    <t>Orientation en enseignement ordinaire</t>
+  </si>
+  <si>
+    <t>11.5</t>
+  </si>
+  <si>
+    <t>Orientation en Etablissement et service d'accompagnement par le travail (ESAT)</t>
+  </si>
+  <si>
+    <t>11.2</t>
+  </si>
+  <si>
+    <t>Orientation en Etablissement ou service de préorientation (ESPO)</t>
+  </si>
+  <si>
+    <t>11.1</t>
+  </si>
+  <si>
+    <t>Orientation en Etablissement ou service de réadaptation professionnelle (ESRP)</t>
+  </si>
+  <si>
+    <t>8.6</t>
+  </si>
+  <si>
+    <t>Orientation en Unité d'enseignement</t>
+  </si>
+  <si>
+    <t>8.4</t>
+  </si>
+  <si>
+    <t>Orientation en Unité localisée pour l'inclusion scolaire (ULIS)</t>
+  </si>
+  <si>
+    <t>11.3</t>
+  </si>
+  <si>
+    <t>Orientation vers l'unité d'évaluation, de réentrainement et d'orientation sociale et socioprofessionnelle pour personnes cérébro-lésées (UEROS)</t>
+  </si>
+  <si>
+    <t>7.7</t>
+  </si>
+  <si>
+    <t>Orientation vers le dispositif ITEP</t>
+  </si>
+  <si>
+    <t>7.12</t>
+  </si>
+  <si>
+    <t>Orientation vers Service de soins et d'aide à domicile (SSAD)</t>
+  </si>
+  <si>
+    <t>13.99</t>
+  </si>
+  <si>
+    <t>Orientation vers un autre établissement ou service médico-social Adultes</t>
+  </si>
+  <si>
+    <t>7.99</t>
+  </si>
+  <si>
+    <t>Orientation vers un autre établissement ou service médico-social Enfants</t>
+  </si>
+  <si>
+    <t>13.2</t>
+  </si>
+  <si>
+    <t>Orientation vers un Etablissement d'accueil médicalisé en tout ou partie</t>
+  </si>
+  <si>
+    <t>13.1</t>
+  </si>
+  <si>
+    <t>Orientation vers un Etablissement d'accueil non médicalisé</t>
+  </si>
+  <si>
+    <t>7.2</t>
+  </si>
+  <si>
+    <t>Orientation vers un Institut d'éducation motrice (IEM)</t>
+  </si>
+  <si>
+    <t>7.13</t>
+  </si>
+  <si>
+    <t>Orientation vers un Institut d'éducation sensorielle (IES)</t>
+  </si>
+  <si>
+    <t>7.1</t>
+  </si>
+  <si>
+    <t>Orientation vers un Institut médico-éducatif (IME)</t>
+  </si>
+  <si>
+    <t>7.3</t>
+  </si>
+  <si>
+    <t>Orientation vers un institut pour personnes avec une déficience auditive</t>
+  </si>
+  <si>
+    <t>7.4</t>
+  </si>
+  <si>
+    <t>Orientation vers un institut pour personnes avec une déficience visuelle</t>
+  </si>
+  <si>
+    <t>7.6</t>
+  </si>
+  <si>
+    <t>Orientation vers un Institut thérapeutique, éducatif et pédagogique (ITEP)</t>
+  </si>
+  <si>
+    <t>8.9</t>
+  </si>
+  <si>
+    <t>Orientation vers un Pôle d'enseignement jeune sourd (PEJS)</t>
+  </si>
+  <si>
+    <t>7.9</t>
+  </si>
+  <si>
+    <t>Orientation vers un Service d'accompagnement familial et d'éducation précoce (SAFEP)</t>
+  </si>
+  <si>
+    <t>13.5</t>
+  </si>
+  <si>
+    <t>Orientation vers un Service d'accompagnement médico-social pour adultes handicapés (SAMSAH)</t>
+  </si>
+  <si>
+    <t>13.4</t>
+  </si>
+  <si>
+    <t>Orientation vers un Service d'accompagnement à la vie sociale (SAVS)</t>
+  </si>
+  <si>
+    <t>7.11</t>
+  </si>
+  <si>
+    <t>Orientation vers un Service d'aide à l'acquisition de l'autonomie et à la scolarisation (SAAAS)</t>
+  </si>
+  <si>
+    <t>7.8</t>
+  </si>
+  <si>
+    <t>Orientation vers un Service d'éducation spéciale et de soins à domicile (SESSAD)</t>
+  </si>
+  <si>
+    <t>7.10</t>
+  </si>
+  <si>
+    <t>Orientation vers un Service de soutien à l'éducation familiale et à la scolarisation (SSEFS)</t>
+  </si>
+  <si>
+    <t>8.11</t>
+  </si>
+  <si>
+    <t>Orientation vers un établissement d'autorégulation</t>
+  </si>
+  <si>
+    <t>7.5</t>
+  </si>
+  <si>
+    <t>Orientation vers un établissement pour enfants ou adolescents polyhandicapés</t>
+  </si>
+  <si>
+    <t>13.3</t>
+  </si>
+  <si>
+    <t>Orientation vers une Maison d'accueil spécialisée (MAS)</t>
+  </si>
+  <si>
+    <t>11.6</t>
+  </si>
+  <si>
+    <t>Orientation vers une plateforme d'emploi accompagné</t>
+  </si>
+  <si>
+    <t>8.7</t>
+  </si>
+  <si>
+    <t>Orientation vers une Scolarisation en milieu ordinaire à temps partagé (UE et établissement scolaire)</t>
+  </si>
+  <si>
+    <t>8.10</t>
+  </si>
+  <si>
+    <t>Orientation vers une unité d'enseignement et une scolarisation en enseignement adapté à temps partagé</t>
+  </si>
+  <si>
+    <t>8.8</t>
+  </si>
+  <si>
+    <t>Orientation vers une Unité d'enseignement et une scolarisation en ULIS à temps partagé</t>
+  </si>
+  <si>
+    <t>5.1</t>
+  </si>
+  <si>
+    <t>PCH - élément 1 - Aide humaine</t>
+  </si>
+  <si>
+    <t>5.2</t>
+  </si>
+  <si>
+    <t>PCH - élément 2 - Aides techniques</t>
+  </si>
+  <si>
+    <t>5.3</t>
+  </si>
+  <si>
+    <t>PCH - élément 3 - Aménagement du logement</t>
+  </si>
+  <si>
+    <t>5.4</t>
+  </si>
+  <si>
+    <t>PCH - élément 3 - Aménagement du véhicule</t>
+  </si>
+  <si>
+    <t>5.5</t>
+  </si>
+  <si>
+    <t>PCH - élément 3 - Surcoûts liés au transport</t>
+  </si>
+  <si>
+    <t>5.7</t>
+  </si>
+  <si>
+    <t>PCH - élément 4 - Charges exceptionnelles</t>
+  </si>
+  <si>
+    <t>5.6</t>
+  </si>
+  <si>
+    <t>PCH - élément 4 - Charges spécifiques</t>
+  </si>
+  <si>
+    <t>5.8</t>
+  </si>
+  <si>
+    <t>PCH - élément 5 - Aide animalière</t>
+  </si>
+  <si>
+    <t>5.9</t>
+  </si>
+  <si>
+    <t>PCH 1 - Aide humaine à la parentalité</t>
+  </si>
+  <si>
+    <t>5.10</t>
+  </si>
+  <si>
+    <t>PCH 2 - Aides techniques à la parentalité</t>
+  </si>
+  <si>
+    <t>8.2</t>
+  </si>
+  <si>
+    <t>Redoublement en maternelle</t>
   </si>
 </sst>
 </file>
@@ -429,4 +839,1381 @@
   </sheetData>
   <pageMargins bottom="0.75" footer="0.3" header="0.3" left="0.7" right="0.7" top="0.75"/>
 </worksheet>
+</file>
+
+<file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <dimension ref="A1:B4"/>
+  <sheetFormatPr defaultRowHeight="15.0"/>
+  <sheetData>
+    <row r="1">
+      <c r="A1" t="s" s="1">
+        <v>35</v>
+      </c>
+      <c r="B1" t="s" s="1">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" t="s" s="2">
+        <v>36</v>
+      </c>
+      <c r="B2" t="s" s="2">
+        <v>37</v>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" t="s" s="2">
+        <v>38</v>
+      </c>
+      <c r="B3" t="s" s="2">
+        <v>37</v>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" t="s" s="2">
+        <v>39</v>
+      </c>
+      <c r="B4" t="s" s="2">
+        <v>37</v>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins bottom="0.75" footer="0.3" header="0.3" left="0.7" right="0.7" top="0.75"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <dimension ref="A1:G63"/>
+  <sheetFormatPr defaultRowHeight="15.0"/>
+  <sheetData>
+    <row r="1">
+      <c r="A1" t="s" s="1">
+        <v>40</v>
+      </c>
+      <c r="B1" t="s" s="1">
+        <v>41</v>
+      </c>
+      <c r="C1" t="s" s="1">
+        <v>38</v>
+      </c>
+      <c r="D1" t="s" s="1">
+        <v>42</v>
+      </c>
+      <c r="E1" t="s" s="1">
+        <v>43</v>
+      </c>
+      <c r="F1" t="s" s="1">
+        <v>44</v>
+      </c>
+      <c r="G1" t="s" s="1">
+        <v>45</v>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" t="s" s="2">
+        <v>46</v>
+      </c>
+      <c r="B2" t="s" s="2">
+        <v>34</v>
+      </c>
+      <c r="C2" s="2"/>
+      <c r="D2" t="s" s="2">
+        <v>47</v>
+      </c>
+      <c r="E2" t="s" s="2">
+        <v>48</v>
+      </c>
+      <c r="F2" t="s" s="2">
+        <v>15</v>
+      </c>
+      <c r="G2" t="s" s="2">
+        <v>15</v>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" t="s" s="2">
+        <v>46</v>
+      </c>
+      <c r="B3" t="s" s="2">
+        <v>34</v>
+      </c>
+      <c r="C3" s="2"/>
+      <c r="D3" t="s" s="2">
+        <v>49</v>
+      </c>
+      <c r="E3" t="s" s="2">
+        <v>50</v>
+      </c>
+      <c r="F3" t="s" s="2">
+        <v>15</v>
+      </c>
+      <c r="G3" t="s" s="2">
+        <v>15</v>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" t="s" s="2">
+        <v>46</v>
+      </c>
+      <c r="B4" t="s" s="2">
+        <v>34</v>
+      </c>
+      <c r="C4" s="2"/>
+      <c r="D4" t="s" s="2">
+        <v>51</v>
+      </c>
+      <c r="E4" t="s" s="2">
+        <v>52</v>
+      </c>
+      <c r="F4" t="s" s="2">
+        <v>15</v>
+      </c>
+      <c r="G4" t="s" s="2">
+        <v>15</v>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" t="s" s="2">
+        <v>46</v>
+      </c>
+      <c r="B5" t="s" s="2">
+        <v>34</v>
+      </c>
+      <c r="C5" s="2"/>
+      <c r="D5" t="s" s="2">
+        <v>53</v>
+      </c>
+      <c r="E5" t="s" s="2">
+        <v>54</v>
+      </c>
+      <c r="F5" t="s" s="2">
+        <v>15</v>
+      </c>
+      <c r="G5" t="s" s="2">
+        <v>15</v>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" t="s" s="2">
+        <v>46</v>
+      </c>
+      <c r="B6" t="s" s="2">
+        <v>34</v>
+      </c>
+      <c r="C6" s="2"/>
+      <c r="D6" t="s" s="2">
+        <v>55</v>
+      </c>
+      <c r="E6" t="s" s="2">
+        <v>56</v>
+      </c>
+      <c r="F6" t="s" s="2">
+        <v>15</v>
+      </c>
+      <c r="G6" t="s" s="2">
+        <v>15</v>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" t="s" s="2">
+        <v>46</v>
+      </c>
+      <c r="B7" t="s" s="2">
+        <v>34</v>
+      </c>
+      <c r="C7" s="2"/>
+      <c r="D7" t="s" s="2">
+        <v>57</v>
+      </c>
+      <c r="E7" t="s" s="2">
+        <v>58</v>
+      </c>
+      <c r="F7" t="s" s="2">
+        <v>15</v>
+      </c>
+      <c r="G7" t="s" s="2">
+        <v>15</v>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" t="s" s="2">
+        <v>46</v>
+      </c>
+      <c r="B8" t="s" s="2">
+        <v>34</v>
+      </c>
+      <c r="C8" s="2"/>
+      <c r="D8" t="s" s="2">
+        <v>59</v>
+      </c>
+      <c r="E8" t="s" s="2">
+        <v>60</v>
+      </c>
+      <c r="F8" t="s" s="2">
+        <v>15</v>
+      </c>
+      <c r="G8" t="s" s="2">
+        <v>15</v>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" t="s" s="2">
+        <v>46</v>
+      </c>
+      <c r="B9" t="s" s="2">
+        <v>34</v>
+      </c>
+      <c r="C9" s="2"/>
+      <c r="D9" t="s" s="2">
+        <v>61</v>
+      </c>
+      <c r="E9" t="s" s="2">
+        <v>62</v>
+      </c>
+      <c r="F9" t="s" s="2">
+        <v>15</v>
+      </c>
+      <c r="G9" t="s" s="2">
+        <v>15</v>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" t="s" s="2">
+        <v>46</v>
+      </c>
+      <c r="B10" t="s" s="2">
+        <v>34</v>
+      </c>
+      <c r="C10" s="2"/>
+      <c r="D10" t="s" s="2">
+        <v>63</v>
+      </c>
+      <c r="E10" t="s" s="2">
+        <v>64</v>
+      </c>
+      <c r="F10" t="s" s="2">
+        <v>15</v>
+      </c>
+      <c r="G10" t="s" s="2">
+        <v>15</v>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" t="s" s="2">
+        <v>46</v>
+      </c>
+      <c r="B11" t="s" s="2">
+        <v>34</v>
+      </c>
+      <c r="C11" s="2"/>
+      <c r="D11" t="s" s="2">
+        <v>65</v>
+      </c>
+      <c r="E11" t="s" s="2">
+        <v>66</v>
+      </c>
+      <c r="F11" t="s" s="2">
+        <v>15</v>
+      </c>
+      <c r="G11" t="s" s="2">
+        <v>15</v>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" t="s" s="2">
+        <v>46</v>
+      </c>
+      <c r="B12" t="s" s="2">
+        <v>34</v>
+      </c>
+      <c r="C12" s="2"/>
+      <c r="D12" t="s" s="2">
+        <v>67</v>
+      </c>
+      <c r="E12" t="s" s="2">
+        <v>68</v>
+      </c>
+      <c r="F12" t="s" s="2">
+        <v>15</v>
+      </c>
+      <c r="G12" t="s" s="2">
+        <v>15</v>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" t="s" s="2">
+        <v>46</v>
+      </c>
+      <c r="B13" t="s" s="2">
+        <v>34</v>
+      </c>
+      <c r="C13" s="2"/>
+      <c r="D13" t="s" s="2">
+        <v>69</v>
+      </c>
+      <c r="E13" t="s" s="2">
+        <v>70</v>
+      </c>
+      <c r="F13" t="s" s="2">
+        <v>15</v>
+      </c>
+      <c r="G13" t="s" s="2">
+        <v>15</v>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" t="s" s="2">
+        <v>46</v>
+      </c>
+      <c r="B14" t="s" s="2">
+        <v>34</v>
+      </c>
+      <c r="C14" s="2"/>
+      <c r="D14" t="s" s="2">
+        <v>71</v>
+      </c>
+      <c r="E14" t="s" s="2">
+        <v>72</v>
+      </c>
+      <c r="F14" t="s" s="2">
+        <v>15</v>
+      </c>
+      <c r="G14" t="s" s="2">
+        <v>15</v>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" t="s" s="2">
+        <v>46</v>
+      </c>
+      <c r="B15" t="s" s="2">
+        <v>34</v>
+      </c>
+      <c r="C15" s="2"/>
+      <c r="D15" t="s" s="2">
+        <v>73</v>
+      </c>
+      <c r="E15" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="F15" t="s" s="2">
+        <v>15</v>
+      </c>
+      <c r="G15" t="s" s="2">
+        <v>15</v>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" t="s" s="2">
+        <v>46</v>
+      </c>
+      <c r="B16" t="s" s="2">
+        <v>34</v>
+      </c>
+      <c r="C16" s="2"/>
+      <c r="D16" t="s" s="2">
+        <v>75</v>
+      </c>
+      <c r="E16" t="s" s="2">
+        <v>76</v>
+      </c>
+      <c r="F16" t="s" s="2">
+        <v>15</v>
+      </c>
+      <c r="G16" t="s" s="2">
+        <v>15</v>
+      </c>
+    </row>
+    <row r="17">
+      <c r="A17" t="s" s="2">
+        <v>46</v>
+      </c>
+      <c r="B17" t="s" s="2">
+        <v>34</v>
+      </c>
+      <c r="C17" s="2"/>
+      <c r="D17" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="E17" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="F17" t="s" s="2">
+        <v>15</v>
+      </c>
+      <c r="G17" t="s" s="2">
+        <v>15</v>
+      </c>
+    </row>
+    <row r="18">
+      <c r="A18" t="s" s="2">
+        <v>46</v>
+      </c>
+      <c r="B18" t="s" s="2">
+        <v>34</v>
+      </c>
+      <c r="C18" s="2"/>
+      <c r="D18" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="E18" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="F18" t="s" s="2">
+        <v>15</v>
+      </c>
+      <c r="G18" t="s" s="2">
+        <v>15</v>
+      </c>
+    </row>
+    <row r="19">
+      <c r="A19" t="s" s="2">
+        <v>46</v>
+      </c>
+      <c r="B19" t="s" s="2">
+        <v>34</v>
+      </c>
+      <c r="C19" s="2"/>
+      <c r="D19" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="E19" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="F19" t="s" s="2">
+        <v>15</v>
+      </c>
+      <c r="G19" t="s" s="2">
+        <v>15</v>
+      </c>
+    </row>
+    <row r="20">
+      <c r="A20" t="s" s="2">
+        <v>46</v>
+      </c>
+      <c r="B20" t="s" s="2">
+        <v>34</v>
+      </c>
+      <c r="C20" s="2"/>
+      <c r="D20" t="s" s="2">
+        <v>83</v>
+      </c>
+      <c r="E20" t="s" s="2">
+        <v>84</v>
+      </c>
+      <c r="F20" t="s" s="2">
+        <v>15</v>
+      </c>
+      <c r="G20" t="s" s="2">
+        <v>15</v>
+      </c>
+    </row>
+    <row r="21">
+      <c r="A21" t="s" s="2">
+        <v>46</v>
+      </c>
+      <c r="B21" t="s" s="2">
+        <v>34</v>
+      </c>
+      <c r="C21" s="2"/>
+      <c r="D21" t="s" s="2">
+        <v>85</v>
+      </c>
+      <c r="E21" t="s" s="2">
+        <v>86</v>
+      </c>
+      <c r="F21" t="s" s="2">
+        <v>15</v>
+      </c>
+      <c r="G21" t="s" s="2">
+        <v>15</v>
+      </c>
+    </row>
+    <row r="22">
+      <c r="A22" t="s" s="2">
+        <v>46</v>
+      </c>
+      <c r="B22" t="s" s="2">
+        <v>34</v>
+      </c>
+      <c r="C22" s="2"/>
+      <c r="D22" t="s" s="2">
+        <v>87</v>
+      </c>
+      <c r="E22" t="s" s="2">
+        <v>88</v>
+      </c>
+      <c r="F22" t="s" s="2">
+        <v>15</v>
+      </c>
+      <c r="G22" t="s" s="2">
+        <v>15</v>
+      </c>
+    </row>
+    <row r="23">
+      <c r="A23" t="s" s="2">
+        <v>46</v>
+      </c>
+      <c r="B23" t="s" s="2">
+        <v>34</v>
+      </c>
+      <c r="C23" s="2"/>
+      <c r="D23" t="s" s="2">
+        <v>89</v>
+      </c>
+      <c r="E23" t="s" s="2">
+        <v>90</v>
+      </c>
+      <c r="F23" t="s" s="2">
+        <v>15</v>
+      </c>
+      <c r="G23" t="s" s="2">
+        <v>15</v>
+      </c>
+    </row>
+    <row r="24">
+      <c r="A24" t="s" s="2">
+        <v>46</v>
+      </c>
+      <c r="B24" t="s" s="2">
+        <v>34</v>
+      </c>
+      <c r="C24" s="2"/>
+      <c r="D24" t="s" s="2">
+        <v>91</v>
+      </c>
+      <c r="E24" t="s" s="2">
+        <v>92</v>
+      </c>
+      <c r="F24" t="s" s="2">
+        <v>15</v>
+      </c>
+      <c r="G24" t="s" s="2">
+        <v>15</v>
+      </c>
+    </row>
+    <row r="25">
+      <c r="A25" t="s" s="2">
+        <v>46</v>
+      </c>
+      <c r="B25" t="s" s="2">
+        <v>34</v>
+      </c>
+      <c r="C25" s="2"/>
+      <c r="D25" t="s" s="2">
+        <v>93</v>
+      </c>
+      <c r="E25" t="s" s="2">
+        <v>94</v>
+      </c>
+      <c r="F25" t="s" s="2">
+        <v>15</v>
+      </c>
+      <c r="G25" t="s" s="2">
+        <v>15</v>
+      </c>
+    </row>
+    <row r="26">
+      <c r="A26" t="s" s="2">
+        <v>46</v>
+      </c>
+      <c r="B26" t="s" s="2">
+        <v>34</v>
+      </c>
+      <c r="C26" s="2"/>
+      <c r="D26" t="s" s="2">
+        <v>95</v>
+      </c>
+      <c r="E26" t="s" s="2">
+        <v>96</v>
+      </c>
+      <c r="F26" t="s" s="2">
+        <v>15</v>
+      </c>
+      <c r="G26" t="s" s="2">
+        <v>15</v>
+      </c>
+    </row>
+    <row r="27">
+      <c r="A27" t="s" s="2">
+        <v>46</v>
+      </c>
+      <c r="B27" t="s" s="2">
+        <v>34</v>
+      </c>
+      <c r="C27" s="2"/>
+      <c r="D27" t="s" s="2">
+        <v>97</v>
+      </c>
+      <c r="E27" t="s" s="2">
+        <v>98</v>
+      </c>
+      <c r="F27" t="s" s="2">
+        <v>15</v>
+      </c>
+      <c r="G27" t="s" s="2">
+        <v>15</v>
+      </c>
+    </row>
+    <row r="28">
+      <c r="A28" t="s" s="2">
+        <v>46</v>
+      </c>
+      <c r="B28" t="s" s="2">
+        <v>34</v>
+      </c>
+      <c r="C28" s="2"/>
+      <c r="D28" t="s" s="2">
+        <v>99</v>
+      </c>
+      <c r="E28" t="s" s="2">
+        <v>100</v>
+      </c>
+      <c r="F28" t="s" s="2">
+        <v>15</v>
+      </c>
+      <c r="G28" t="s" s="2">
+        <v>15</v>
+      </c>
+    </row>
+    <row r="29">
+      <c r="A29" t="s" s="2">
+        <v>46</v>
+      </c>
+      <c r="B29" t="s" s="2">
+        <v>34</v>
+      </c>
+      <c r="C29" s="2"/>
+      <c r="D29" t="s" s="2">
+        <v>101</v>
+      </c>
+      <c r="E29" t="s" s="2">
+        <v>102</v>
+      </c>
+      <c r="F29" t="s" s="2">
+        <v>15</v>
+      </c>
+      <c r="G29" t="s" s="2">
+        <v>15</v>
+      </c>
+    </row>
+    <row r="30">
+      <c r="A30" t="s" s="2">
+        <v>46</v>
+      </c>
+      <c r="B30" t="s" s="2">
+        <v>34</v>
+      </c>
+      <c r="C30" s="2"/>
+      <c r="D30" t="s" s="2">
+        <v>103</v>
+      </c>
+      <c r="E30" t="s" s="2">
+        <v>104</v>
+      </c>
+      <c r="F30" t="s" s="2">
+        <v>15</v>
+      </c>
+      <c r="G30" t="s" s="2">
+        <v>15</v>
+      </c>
+    </row>
+    <row r="31">
+      <c r="A31" t="s" s="2">
+        <v>46</v>
+      </c>
+      <c r="B31" t="s" s="2">
+        <v>34</v>
+      </c>
+      <c r="C31" s="2"/>
+      <c r="D31" t="s" s="2">
+        <v>105</v>
+      </c>
+      <c r="E31" t="s" s="2">
+        <v>106</v>
+      </c>
+      <c r="F31" t="s" s="2">
+        <v>15</v>
+      </c>
+      <c r="G31" t="s" s="2">
+        <v>15</v>
+      </c>
+    </row>
+    <row r="32">
+      <c r="A32" t="s" s="2">
+        <v>46</v>
+      </c>
+      <c r="B32" t="s" s="2">
+        <v>34</v>
+      </c>
+      <c r="C32" s="2"/>
+      <c r="D32" t="s" s="2">
+        <v>107</v>
+      </c>
+      <c r="E32" t="s" s="2">
+        <v>108</v>
+      </c>
+      <c r="F32" t="s" s="2">
+        <v>15</v>
+      </c>
+      <c r="G32" t="s" s="2">
+        <v>15</v>
+      </c>
+    </row>
+    <row r="33">
+      <c r="A33" t="s" s="2">
+        <v>46</v>
+      </c>
+      <c r="B33" t="s" s="2">
+        <v>34</v>
+      </c>
+      <c r="C33" s="2"/>
+      <c r="D33" t="s" s="2">
+        <v>109</v>
+      </c>
+      <c r="E33" t="s" s="2">
+        <v>110</v>
+      </c>
+      <c r="F33" t="s" s="2">
+        <v>15</v>
+      </c>
+      <c r="G33" t="s" s="2">
+        <v>15</v>
+      </c>
+    </row>
+    <row r="34">
+      <c r="A34" t="s" s="2">
+        <v>46</v>
+      </c>
+      <c r="B34" t="s" s="2">
+        <v>34</v>
+      </c>
+      <c r="C34" s="2"/>
+      <c r="D34" t="s" s="2">
+        <v>111</v>
+      </c>
+      <c r="E34" t="s" s="2">
+        <v>112</v>
+      </c>
+      <c r="F34" t="s" s="2">
+        <v>15</v>
+      </c>
+      <c r="G34" t="s" s="2">
+        <v>15</v>
+      </c>
+    </row>
+    <row r="35">
+      <c r="A35" t="s" s="2">
+        <v>46</v>
+      </c>
+      <c r="B35" t="s" s="2">
+        <v>34</v>
+      </c>
+      <c r="C35" s="2"/>
+      <c r="D35" t="s" s="2">
+        <v>113</v>
+      </c>
+      <c r="E35" t="s" s="2">
+        <v>114</v>
+      </c>
+      <c r="F35" t="s" s="2">
+        <v>15</v>
+      </c>
+      <c r="G35" t="s" s="2">
+        <v>15</v>
+      </c>
+    </row>
+    <row r="36">
+      <c r="A36" t="s" s="2">
+        <v>46</v>
+      </c>
+      <c r="B36" t="s" s="2">
+        <v>34</v>
+      </c>
+      <c r="C36" s="2"/>
+      <c r="D36" t="s" s="2">
+        <v>115</v>
+      </c>
+      <c r="E36" t="s" s="2">
+        <v>116</v>
+      </c>
+      <c r="F36" t="s" s="2">
+        <v>15</v>
+      </c>
+      <c r="G36" t="s" s="2">
+        <v>15</v>
+      </c>
+    </row>
+    <row r="37">
+      <c r="A37" t="s" s="2">
+        <v>46</v>
+      </c>
+      <c r="B37" t="s" s="2">
+        <v>34</v>
+      </c>
+      <c r="C37" s="2"/>
+      <c r="D37" t="s" s="2">
+        <v>117</v>
+      </c>
+      <c r="E37" t="s" s="2">
+        <v>118</v>
+      </c>
+      <c r="F37" t="s" s="2">
+        <v>15</v>
+      </c>
+      <c r="G37" t="s" s="2">
+        <v>15</v>
+      </c>
+    </row>
+    <row r="38">
+      <c r="A38" t="s" s="2">
+        <v>46</v>
+      </c>
+      <c r="B38" t="s" s="2">
+        <v>34</v>
+      </c>
+      <c r="C38" s="2"/>
+      <c r="D38" t="s" s="2">
+        <v>119</v>
+      </c>
+      <c r="E38" t="s" s="2">
+        <v>120</v>
+      </c>
+      <c r="F38" t="s" s="2">
+        <v>15</v>
+      </c>
+      <c r="G38" t="s" s="2">
+        <v>15</v>
+      </c>
+    </row>
+    <row r="39">
+      <c r="A39" t="s" s="2">
+        <v>46</v>
+      </c>
+      <c r="B39" t="s" s="2">
+        <v>34</v>
+      </c>
+      <c r="C39" s="2"/>
+      <c r="D39" t="s" s="2">
+        <v>121</v>
+      </c>
+      <c r="E39" t="s" s="2">
+        <v>122</v>
+      </c>
+      <c r="F39" t="s" s="2">
+        <v>15</v>
+      </c>
+      <c r="G39" t="s" s="2">
+        <v>15</v>
+      </c>
+    </row>
+    <row r="40">
+      <c r="A40" t="s" s="2">
+        <v>46</v>
+      </c>
+      <c r="B40" t="s" s="2">
+        <v>34</v>
+      </c>
+      <c r="C40" s="2"/>
+      <c r="D40" t="s" s="2">
+        <v>123</v>
+      </c>
+      <c r="E40" t="s" s="2">
+        <v>124</v>
+      </c>
+      <c r="F40" t="s" s="2">
+        <v>15</v>
+      </c>
+      <c r="G40" t="s" s="2">
+        <v>15</v>
+      </c>
+    </row>
+    <row r="41">
+      <c r="A41" t="s" s="2">
+        <v>46</v>
+      </c>
+      <c r="B41" t="s" s="2">
+        <v>34</v>
+      </c>
+      <c r="C41" s="2"/>
+      <c r="D41" t="s" s="2">
+        <v>125</v>
+      </c>
+      <c r="E41" t="s" s="2">
+        <v>126</v>
+      </c>
+      <c r="F41" t="s" s="2">
+        <v>15</v>
+      </c>
+      <c r="G41" t="s" s="2">
+        <v>15</v>
+      </c>
+    </row>
+    <row r="42">
+      <c r="A42" t="s" s="2">
+        <v>46</v>
+      </c>
+      <c r="B42" t="s" s="2">
+        <v>34</v>
+      </c>
+      <c r="C42" s="2"/>
+      <c r="D42" t="s" s="2">
+        <v>127</v>
+      </c>
+      <c r="E42" t="s" s="2">
+        <v>128</v>
+      </c>
+      <c r="F42" t="s" s="2">
+        <v>15</v>
+      </c>
+      <c r="G42" t="s" s="2">
+        <v>15</v>
+      </c>
+    </row>
+    <row r="43">
+      <c r="A43" t="s" s="2">
+        <v>46</v>
+      </c>
+      <c r="B43" t="s" s="2">
+        <v>34</v>
+      </c>
+      <c r="C43" s="2"/>
+      <c r="D43" t="s" s="2">
+        <v>129</v>
+      </c>
+      <c r="E43" t="s" s="2">
+        <v>130</v>
+      </c>
+      <c r="F43" t="s" s="2">
+        <v>15</v>
+      </c>
+      <c r="G43" t="s" s="2">
+        <v>15</v>
+      </c>
+    </row>
+    <row r="44">
+      <c r="A44" t="s" s="2">
+        <v>46</v>
+      </c>
+      <c r="B44" t="s" s="2">
+        <v>34</v>
+      </c>
+      <c r="C44" s="2"/>
+      <c r="D44" t="s" s="2">
+        <v>131</v>
+      </c>
+      <c r="E44" t="s" s="2">
+        <v>132</v>
+      </c>
+      <c r="F44" t="s" s="2">
+        <v>15</v>
+      </c>
+      <c r="G44" t="s" s="2">
+        <v>15</v>
+      </c>
+    </row>
+    <row r="45">
+      <c r="A45" t="s" s="2">
+        <v>46</v>
+      </c>
+      <c r="B45" t="s" s="2">
+        <v>34</v>
+      </c>
+      <c r="C45" s="2"/>
+      <c r="D45" t="s" s="2">
+        <v>133</v>
+      </c>
+      <c r="E45" t="s" s="2">
+        <v>134</v>
+      </c>
+      <c r="F45" t="s" s="2">
+        <v>15</v>
+      </c>
+      <c r="G45" t="s" s="2">
+        <v>15</v>
+      </c>
+    </row>
+    <row r="46">
+      <c r="A46" t="s" s="2">
+        <v>46</v>
+      </c>
+      <c r="B46" t="s" s="2">
+        <v>34</v>
+      </c>
+      <c r="C46" s="2"/>
+      <c r="D46" t="s" s="2">
+        <v>135</v>
+      </c>
+      <c r="E46" t="s" s="2">
+        <v>136</v>
+      </c>
+      <c r="F46" t="s" s="2">
+        <v>15</v>
+      </c>
+      <c r="G46" t="s" s="2">
+        <v>15</v>
+      </c>
+    </row>
+    <row r="47">
+      <c r="A47" t="s" s="2">
+        <v>46</v>
+      </c>
+      <c r="B47" t="s" s="2">
+        <v>34</v>
+      </c>
+      <c r="C47" s="2"/>
+      <c r="D47" t="s" s="2">
+        <v>137</v>
+      </c>
+      <c r="E47" t="s" s="2">
+        <v>138</v>
+      </c>
+      <c r="F47" t="s" s="2">
+        <v>15</v>
+      </c>
+      <c r="G47" t="s" s="2">
+        <v>15</v>
+      </c>
+    </row>
+    <row r="48">
+      <c r="A48" t="s" s="2">
+        <v>46</v>
+      </c>
+      <c r="B48" t="s" s="2">
+        <v>34</v>
+      </c>
+      <c r="C48" s="2"/>
+      <c r="D48" t="s" s="2">
+        <v>139</v>
+      </c>
+      <c r="E48" t="s" s="2">
+        <v>140</v>
+      </c>
+      <c r="F48" t="s" s="2">
+        <v>15</v>
+      </c>
+      <c r="G48" t="s" s="2">
+        <v>15</v>
+      </c>
+    </row>
+    <row r="49">
+      <c r="A49" t="s" s="2">
+        <v>46</v>
+      </c>
+      <c r="B49" t="s" s="2">
+        <v>34</v>
+      </c>
+      <c r="C49" s="2"/>
+      <c r="D49" t="s" s="2">
+        <v>141</v>
+      </c>
+      <c r="E49" t="s" s="2">
+        <v>142</v>
+      </c>
+      <c r="F49" t="s" s="2">
+        <v>15</v>
+      </c>
+      <c r="G49" t="s" s="2">
+        <v>15</v>
+      </c>
+    </row>
+    <row r="50">
+      <c r="A50" t="s" s="2">
+        <v>46</v>
+      </c>
+      <c r="B50" t="s" s="2">
+        <v>34</v>
+      </c>
+      <c r="C50" s="2"/>
+      <c r="D50" t="s" s="2">
+        <v>143</v>
+      </c>
+      <c r="E50" t="s" s="2">
+        <v>144</v>
+      </c>
+      <c r="F50" t="s" s="2">
+        <v>15</v>
+      </c>
+      <c r="G50" t="s" s="2">
+        <v>15</v>
+      </c>
+    </row>
+    <row r="51">
+      <c r="A51" t="s" s="2">
+        <v>46</v>
+      </c>
+      <c r="B51" t="s" s="2">
+        <v>34</v>
+      </c>
+      <c r="C51" s="2"/>
+      <c r="D51" t="s" s="2">
+        <v>145</v>
+      </c>
+      <c r="E51" t="s" s="2">
+        <v>146</v>
+      </c>
+      <c r="F51" t="s" s="2">
+        <v>15</v>
+      </c>
+      <c r="G51" t="s" s="2">
+        <v>15</v>
+      </c>
+    </row>
+    <row r="52">
+      <c r="A52" t="s" s="2">
+        <v>46</v>
+      </c>
+      <c r="B52" t="s" s="2">
+        <v>34</v>
+      </c>
+      <c r="C52" s="2"/>
+      <c r="D52" t="s" s="2">
+        <v>147</v>
+      </c>
+      <c r="E52" t="s" s="2">
+        <v>148</v>
+      </c>
+      <c r="F52" t="s" s="2">
+        <v>15</v>
+      </c>
+      <c r="G52" t="s" s="2">
+        <v>15</v>
+      </c>
+    </row>
+    <row r="53">
+      <c r="A53" t="s" s="2">
+        <v>46</v>
+      </c>
+      <c r="B53" t="s" s="2">
+        <v>34</v>
+      </c>
+      <c r="C53" s="2"/>
+      <c r="D53" t="s" s="2">
+        <v>149</v>
+      </c>
+      <c r="E53" t="s" s="2">
+        <v>150</v>
+      </c>
+      <c r="F53" t="s" s="2">
+        <v>15</v>
+      </c>
+      <c r="G53" t="s" s="2">
+        <v>15</v>
+      </c>
+    </row>
+    <row r="54">
+      <c r="A54" t="s" s="2">
+        <v>46</v>
+      </c>
+      <c r="B54" t="s" s="2">
+        <v>34</v>
+      </c>
+      <c r="C54" s="2"/>
+      <c r="D54" t="s" s="2">
+        <v>151</v>
+      </c>
+      <c r="E54" t="s" s="2">
+        <v>152</v>
+      </c>
+      <c r="F54" t="s" s="2">
+        <v>15</v>
+      </c>
+      <c r="G54" t="s" s="2">
+        <v>15</v>
+      </c>
+    </row>
+    <row r="55">
+      <c r="A55" t="s" s="2">
+        <v>46</v>
+      </c>
+      <c r="B55" t="s" s="2">
+        <v>34</v>
+      </c>
+      <c r="C55" s="2"/>
+      <c r="D55" t="s" s="2">
+        <v>153</v>
+      </c>
+      <c r="E55" t="s" s="2">
+        <v>154</v>
+      </c>
+      <c r="F55" t="s" s="2">
+        <v>15</v>
+      </c>
+      <c r="G55" t="s" s="2">
+        <v>15</v>
+      </c>
+    </row>
+    <row r="56">
+      <c r="A56" t="s" s="2">
+        <v>46</v>
+      </c>
+      <c r="B56" t="s" s="2">
+        <v>34</v>
+      </c>
+      <c r="C56" s="2"/>
+      <c r="D56" t="s" s="2">
+        <v>155</v>
+      </c>
+      <c r="E56" t="s" s="2">
+        <v>156</v>
+      </c>
+      <c r="F56" t="s" s="2">
+        <v>15</v>
+      </c>
+      <c r="G56" t="s" s="2">
+        <v>15</v>
+      </c>
+    </row>
+    <row r="57">
+      <c r="A57" t="s" s="2">
+        <v>46</v>
+      </c>
+      <c r="B57" t="s" s="2">
+        <v>34</v>
+      </c>
+      <c r="C57" s="2"/>
+      <c r="D57" t="s" s="2">
+        <v>157</v>
+      </c>
+      <c r="E57" t="s" s="2">
+        <v>158</v>
+      </c>
+      <c r="F57" t="s" s="2">
+        <v>15</v>
+      </c>
+      <c r="G57" t="s" s="2">
+        <v>15</v>
+      </c>
+    </row>
+    <row r="58">
+      <c r="A58" t="s" s="2">
+        <v>46</v>
+      </c>
+      <c r="B58" t="s" s="2">
+        <v>34</v>
+      </c>
+      <c r="C58" s="2"/>
+      <c r="D58" t="s" s="2">
+        <v>159</v>
+      </c>
+      <c r="E58" t="s" s="2">
+        <v>160</v>
+      </c>
+      <c r="F58" t="s" s="2">
+        <v>15</v>
+      </c>
+      <c r="G58" t="s" s="2">
+        <v>15</v>
+      </c>
+    </row>
+    <row r="59">
+      <c r="A59" t="s" s="2">
+        <v>46</v>
+      </c>
+      <c r="B59" t="s" s="2">
+        <v>34</v>
+      </c>
+      <c r="C59" s="2"/>
+      <c r="D59" t="s" s="2">
+        <v>161</v>
+      </c>
+      <c r="E59" t="s" s="2">
+        <v>162</v>
+      </c>
+      <c r="F59" t="s" s="2">
+        <v>15</v>
+      </c>
+      <c r="G59" t="s" s="2">
+        <v>15</v>
+      </c>
+    </row>
+    <row r="60">
+      <c r="A60" t="s" s="2">
+        <v>46</v>
+      </c>
+      <c r="B60" t="s" s="2">
+        <v>34</v>
+      </c>
+      <c r="C60" s="2"/>
+      <c r="D60" t="s" s="2">
+        <v>163</v>
+      </c>
+      <c r="E60" t="s" s="2">
+        <v>164</v>
+      </c>
+      <c r="F60" t="s" s="2">
+        <v>15</v>
+      </c>
+      <c r="G60" t="s" s="2">
+        <v>15</v>
+      </c>
+    </row>
+    <row r="61">
+      <c r="A61" t="s" s="2">
+        <v>46</v>
+      </c>
+      <c r="B61" t="s" s="2">
+        <v>34</v>
+      </c>
+      <c r="C61" s="2"/>
+      <c r="D61" t="s" s="2">
+        <v>165</v>
+      </c>
+      <c r="E61" t="s" s="2">
+        <v>166</v>
+      </c>
+      <c r="F61" t="s" s="2">
+        <v>15</v>
+      </c>
+      <c r="G61" t="s" s="2">
+        <v>15</v>
+      </c>
+    </row>
+    <row r="62">
+      <c r="A62" t="s" s="2">
+        <v>46</v>
+      </c>
+      <c r="B62" t="s" s="2">
+        <v>34</v>
+      </c>
+      <c r="C62" s="2"/>
+      <c r="D62" t="s" s="2">
+        <v>167</v>
+      </c>
+      <c r="E62" t="s" s="2">
+        <v>168</v>
+      </c>
+      <c r="F62" t="s" s="2">
+        <v>15</v>
+      </c>
+      <c r="G62" t="s" s="2">
+        <v>15</v>
+      </c>
+    </row>
+    <row r="63">
+      <c r="A63" t="s" s="2">
+        <v>46</v>
+      </c>
+      <c r="B63" t="s" s="2">
+        <v>34</v>
+      </c>
+      <c r="C63" s="2"/>
+      <c r="D63" t="s" s="2">
+        <v>169</v>
+      </c>
+      <c r="E63" t="s" s="2">
+        <v>170</v>
+      </c>
+      <c r="F63" t="s" s="2">
+        <v>15</v>
+      </c>
+      <c r="G63" t="s" s="2">
+        <v>15</v>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins bottom="0.75" footer="0.3" header="0.3" left="0.7" right="0.7" top="0.75"/>
+</worksheet>
 </file>